--- a/Stanmere_Capital_Partners_I_Master_Case.xlsx
+++ b/Stanmere_Capital_Partners_I_Master_Case.xlsx
@@ -1095,7 +1095,7 @@
     <t xml:space="preserve">    Net change in unrealized (appreciation) / depreciation</t>
   </si>
   <si>
-    <t xml:space="preserve">    PIK interest income capitalised into the note principal (non-cash)</t>
+    <t xml:space="preserve">    PIK interest income capitalized into the note principal (non-cash)</t>
   </si>
   <si>
     <t xml:space="preserve">    Purchases of investments, at cost</t>
